--- a/data-raw/experiment/Pre- %20and%20Post%20Centrifugation%20data%20for%20FS%20and%20fresh%20faeces%20.xlsx
+++ b/data-raw/experiment/Pre- %20and%20Post%20Centrifugation%20data%20for%20FS%20and%20fresh%20faeces%20.xlsx
@@ -1,23 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Addendum Excel files\Dewaterability\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mzhong/Desktop/openwashdata/dryingfaecal/data-raw/experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2992AAFA-BE54-D94C-94BA-BE602FF248F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView minimized="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -158,7 +170,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -815,7 +827,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -913,7 +925,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -946,9 +958,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -957,9 +966,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -975,8 +983,71 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -989,69 +1060,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1073,7 +1081,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1368,7 +1376,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-CH"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1549480688"/>
@@ -1433,7 +1441,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-CH"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1549478192"/>
@@ -1492,7 +1500,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CH"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1522,7 +1530,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="en-CH"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1536,7 +1544,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1819,7 +1827,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-CH"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1549480688"/>
@@ -1884,7 +1892,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-CH"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1549478192"/>
@@ -1943,7 +1951,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CH"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1973,7 +1981,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="en-CH"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1987,7 +1995,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2272,7 +2280,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-CH"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1549480688"/>
@@ -2336,7 +2344,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-CH"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1549478192"/>
@@ -2395,7 +2403,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CH"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -2425,7 +2433,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="en-CH"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2439,7 +2447,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2724,7 +2732,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-CH"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1549480688"/>
@@ -2788,7 +2796,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-CH"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1549478192"/>
@@ -2847,7 +2855,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CH"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -2877,7 +2885,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="en-CH"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -5077,7 +5085,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -5107,7 +5121,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -5139,7 +5159,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -5171,7 +5197,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart 6"/>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -5453,39 +5485,39 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:V35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="3" width="13.42578125" customWidth="1"/>
+    <col min="2" max="3" width="13.5" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" customWidth="1"/>
-    <col min="10" max="10" width="15.28515625" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" customWidth="1"/>
+    <col min="7" max="7" width="14.1640625" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="82" t="s">
+    <row r="1" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="83"/>
-      <c r="G2" s="82" t="s">
+      <c r="F2" s="64"/>
+      <c r="G2" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="83"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="82" t="s">
+      <c r="H2" s="64"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="84"/>
+      <c r="K2" s="65"/>
     </row>
-    <row r="3" spans="2:21" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:21" ht="49" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -5529,20 +5561,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B4" s="74" t="s">
+    <row r="4" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B4" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="74">
+      <c r="C4" s="73">
         <v>88</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="76">
+      <c r="E4" s="75">
         <v>5000</v>
       </c>
-      <c r="F4" s="76">
+      <c r="F4" s="75">
         <v>120</v>
       </c>
       <c r="G4" s="8">
@@ -5560,31 +5592,31 @@
       <c r="K4" s="12">
         <v>72.796999999999997</v>
       </c>
-      <c r="L4" s="68">
+      <c r="L4" s="67">
         <f>AVERAGE(J4,J5,J6)</f>
         <v>0.97350000000000003</v>
       </c>
-      <c r="M4" s="68">
+      <c r="M4" s="67">
         <f>STDEV(J4:J6)/SQRT(COUNT(J4:J6))</f>
         <v>7.2341781380704103E-4</v>
       </c>
-      <c r="N4" s="68">
+      <c r="N4" s="67">
         <f>AVERAGE(K4,K5,K6)</f>
         <v>73.096000000000004</v>
       </c>
-      <c r="O4" s="68">
+      <c r="O4" s="67">
         <f>STDEV(K4:K6)/SQRT(COUNT(K4:K6))</f>
         <v>0.61793554140649487</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
       <c r="D5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
       <c r="G5" s="14">
         <v>24.6798</v>
       </c>
@@ -5600,19 +5632,19 @@
       <c r="K5" s="17">
         <v>72.206999999999994</v>
       </c>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
     </row>
-    <row r="6" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="75"/>
-      <c r="C6" s="75"/>
+    <row r="6" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
       <c r="D6" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
       <c r="G6" s="19">
         <v>24.6249</v>
       </c>
@@ -5628,23 +5660,23 @@
       <c r="K6" s="23">
         <v>74.284000000000006</v>
       </c>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
     </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B7" s="71" t="s">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B7" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="71">
+      <c r="C7" s="70">
         <v>73</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
       <c r="G7" s="9">
         <v>24.630800000000001</v>
       </c>
@@ -5660,31 +5692,31 @@
       <c r="K7" s="24">
         <v>66.686000000000007</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="67">
         <f>AVERAGE(J7,J8,J9)</f>
         <v>0.94210000000000005</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="67">
         <f t="shared" ref="M7" si="0">STDEV(J7:J9)/SQRT(COUNT(J7:J9))</f>
         <v>4.3588989435405329E-4</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="67">
         <f>AVERAGE(K7,K8,K9)</f>
         <v>66.933000000000007</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="67">
         <f t="shared" ref="O7" si="1">STDEV(K7:K9)/SQRT(COUNT(K7:K9))</f>
         <v>0.14347938295564741</v>
       </c>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B8" s="71"/>
+      <c r="C8" s="71"/>
       <c r="D8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
       <c r="G8" s="15">
         <v>24.403099999999998</v>
       </c>
@@ -5700,19 +5732,19 @@
       <c r="K8" s="17">
         <v>67.183000000000007</v>
       </c>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
+      <c r="O8" s="68"/>
     </row>
-    <row r="9" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
+    <row r="9" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="72"/>
+      <c r="C9" s="72"/>
       <c r="D9" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
       <c r="G9" s="22">
         <v>24.613399999999999</v>
       </c>
@@ -5728,23 +5760,23 @@
       <c r="K9" s="23">
         <v>66.930000000000007</v>
       </c>
-      <c r="L9" s="70"/>
-      <c r="M9" s="70"/>
-      <c r="N9" s="70"/>
-      <c r="O9" s="70"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="69"/>
+      <c r="N9" s="69"/>
+      <c r="O9" s="69"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B10" s="79" t="s">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B10" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="79">
+      <c r="C10" s="78">
         <v>72</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
       <c r="G10" s="27">
         <v>24.77</v>
       </c>
@@ -5760,31 +5792,31 @@
       <c r="K10" s="29">
         <v>58.170999999999999</v>
       </c>
-      <c r="L10" s="62">
+      <c r="L10" s="81">
         <f>AVERAGE(J10,J11,J12)</f>
         <v>0.96456666666666668</v>
       </c>
-      <c r="M10" s="62">
+      <c r="M10" s="81">
         <f t="shared" ref="M10" si="2">STDEV(J10:J12)/SQRT(COUNT(J10:J12))</f>
         <v>2.3311894913207675E-3</v>
       </c>
-      <c r="N10" s="62">
+      <c r="N10" s="81">
         <f>AVERAGE(K10,K11,K12)</f>
         <v>57.925333333333334</v>
       </c>
-      <c r="O10" s="62">
+      <c r="O10" s="81">
         <f>STDEV(K10:K12)/SQRT(COUNT(K10:K12))</f>
         <v>0.90299766211091392</v>
       </c>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B11" s="79"/>
+      <c r="C11" s="79"/>
       <c r="D11" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="76"/>
       <c r="G11" s="31">
         <v>24.774799999999999</v>
       </c>
@@ -5800,19 +5832,19 @@
       <c r="K11" s="33">
         <v>56.253</v>
       </c>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="63"/>
-      <c r="O11" s="63"/>
+      <c r="L11" s="82"/>
+      <c r="M11" s="82"/>
+      <c r="N11" s="82"/>
+      <c r="O11" s="82"/>
     </row>
-    <row r="12" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
+    <row r="12" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="80"/>
+      <c r="C12" s="80"/>
       <c r="D12" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
       <c r="G12" s="35">
         <v>24.819199999999999</v>
       </c>
@@ -5828,23 +5860,23 @@
       <c r="K12" s="38">
         <v>59.351999999999997</v>
       </c>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="64"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="83"/>
+      <c r="N12" s="83"/>
+      <c r="O12" s="83"/>
     </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B13" s="65" t="s">
+    <row r="13" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B13" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="65">
+      <c r="C13" s="84">
         <v>80</v>
       </c>
       <c r="D13" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="76"/>
       <c r="G13" s="40">
         <v>24.675899999999999</v>
       </c>
@@ -5860,31 +5892,31 @@
       <c r="K13" s="29">
         <v>76.578000000000003</v>
       </c>
-      <c r="L13" s="62">
+      <c r="L13" s="81">
         <f>AVERAGE(J13,J14,J15)</f>
         <v>0.95223333333333338</v>
       </c>
-      <c r="M13" s="62">
+      <c r="M13" s="81">
         <f t="shared" ref="M13" si="3">STDEV(J13:J15)/SQRT(COUNT(J13:J15))</f>
         <v>3.4226370599940202E-3</v>
       </c>
-      <c r="N13" s="62">
+      <c r="N13" s="81">
         <f>AVERAGE(K13,K14,K15)</f>
         <v>76.483333333333334</v>
       </c>
-      <c r="O13" s="62">
+      <c r="O13" s="81">
         <f t="shared" ref="O13" si="4">STDEV(K13:K15)/SQRT(COUNT(K13:K15))</f>
         <v>8.2010839391987667E-2</v>
       </c>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
       <c r="D14" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
       <c r="G14" s="31">
         <v>24.565899999999999</v>
       </c>
@@ -5897,29 +5929,29 @@
       <c r="J14" s="31">
         <v>0.95779999999999998</v>
       </c>
-      <c r="K14" s="44">
+      <c r="K14" s="33">
         <v>76.552000000000007</v>
       </c>
-      <c r="L14" s="63"/>
-      <c r="M14" s="63"/>
-      <c r="N14" s="63"/>
-      <c r="O14" s="63"/>
+      <c r="L14" s="82"/>
+      <c r="M14" s="82"/>
+      <c r="N14" s="82"/>
+      <c r="O14" s="82"/>
     </row>
-    <row r="15" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="67"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="45" t="s">
+    <row r="15" spans="2:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="80"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
       <c r="G15" s="36">
         <v>24.6417</v>
       </c>
       <c r="H15" s="36">
         <v>63.353700000000003</v>
       </c>
-      <c r="I15" s="46">
+      <c r="I15" s="45">
         <v>54.7318</v>
       </c>
       <c r="J15" s="36">
@@ -5928,239 +5960,238 @@
       <c r="K15" s="38">
         <v>76.319999999999993</v>
       </c>
-      <c r="L15" s="64"/>
-      <c r="M15" s="64"/>
-      <c r="N15" s="64"/>
-      <c r="O15" s="64"/>
+      <c r="L15" s="83"/>
+      <c r="M15" s="83"/>
+      <c r="N15" s="83"/>
+      <c r="O15" s="83"/>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I16" s="85" t="s">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="I16" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="J16" s="85"/>
-      <c r="K16" s="85"/>
-      <c r="L16" s="85"/>
-      <c r="N16" s="86" t="s">
+      <c r="J16" s="66"/>
+      <c r="K16" s="66"/>
+      <c r="L16" s="66"/>
+      <c r="N16" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="O16" s="86"/>
-      <c r="P16" s="86"/>
-      <c r="Q16" s="86"/>
-      <c r="R16" s="86"/>
-      <c r="S16" s="86"/>
-      <c r="T16" s="86"/>
-      <c r="U16" s="86"/>
+      <c r="O16" s="60"/>
+      <c r="P16" s="60"/>
+      <c r="Q16" s="60"/>
+      <c r="R16" s="60"/>
+      <c r="S16" s="60"/>
+      <c r="T16" s="60"/>
+      <c r="U16" s="60"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="47"/>
-      <c r="C17" s="80" t="s">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B17" s="46"/>
+      <c r="C17" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80" t="s">
+      <c r="D17" s="61"/>
+      <c r="E17" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="81"/>
+      <c r="F17" s="62"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="53"/>
-      <c r="C18" s="56" t="s">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B18" s="51"/>
+      <c r="C18" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="57" t="s">
+      <c r="D18" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="56" t="s">
+      <c r="E18" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="58" t="s">
+      <c r="F18" s="56" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="48" t="s">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B19" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="51">
+      <c r="C19" s="49">
         <f>C4/100</f>
         <v>0.88</v>
       </c>
-      <c r="D19" s="61">
+      <c r="D19" s="59">
         <f>N4/100</f>
         <v>0.73096000000000005</v>
       </c>
-      <c r="E19" s="49">
+      <c r="E19">
         <f>97.8/100</f>
         <v>0.97799999999999998</v>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="48">
         <f>L4</f>
         <v>0.97350000000000003</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="48" t="s">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B20" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="51">
+      <c r="C20" s="49">
         <f>C7/100</f>
         <v>0.73</v>
       </c>
-      <c r="D20" s="61">
+      <c r="D20" s="59">
         <f>N7/100</f>
         <v>0.66933000000000009</v>
       </c>
-      <c r="E20" s="49">
+      <c r="E20">
         <v>0.98899999999999999</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="48">
         <f>L7</f>
         <v>0.94210000000000005</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="48" t="s">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B21" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="51">
+      <c r="C21" s="49">
         <f>C10/100</f>
         <v>0.72</v>
       </c>
-      <c r="D21" s="61">
+      <c r="D21" s="59">
         <f>N10/100</f>
         <v>0.5792533333333334</v>
       </c>
-      <c r="E21" s="49">
+      <c r="E21">
         <v>0.98</v>
       </c>
-      <c r="F21" s="52">
+      <c r="F21" s="50">
         <f>L10</f>
         <v>0.96456666666666668</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="53" t="s">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B22" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="60">
+      <c r="C22" s="58">
         <v>0.77776546720505901</v>
       </c>
-      <c r="D22" s="60">
+      <c r="D22" s="58">
         <f>N13/100</f>
         <v>0.76483333333333337</v>
       </c>
-      <c r="E22" s="54">
+      <c r="E22" s="52">
         <v>0.96596666666666697</v>
       </c>
-      <c r="F22" s="55">
+      <c r="F22" s="53">
         <f>L13</f>
         <v>0.95223333333333338</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C24" s="59" t="s">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C24" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C25" s="59">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C25" s="57">
         <v>0.01</v>
       </c>
-      <c r="D25" s="59">
+      <c r="D25" s="57">
         <f>O4/100</f>
         <v>6.1793554140649491E-3</v>
       </c>
-      <c r="E25" s="59">
+      <c r="E25" s="57">
         <v>1.15325625946708E-2</v>
       </c>
-      <c r="F25" s="59">
+      <c r="F25" s="57">
         <f>M4</f>
         <v>7.2341781380704103E-4</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C26" s="59">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C26" s="57">
         <v>0.01</v>
       </c>
-      <c r="D26" s="59">
+      <c r="D26" s="57">
         <f>O7/100</f>
         <v>1.434793829556474E-3</v>
       </c>
-      <c r="E26" s="59">
+      <c r="E26" s="57">
         <v>1.17364105813206E-2</v>
       </c>
-      <c r="F26" s="59">
+      <c r="F26" s="57">
         <f>M7</f>
         <v>4.3588989435405329E-4</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C27" s="59">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C27" s="57">
         <v>0.01</v>
       </c>
-      <c r="D27" s="59">
+      <c r="D27" s="57">
         <f>O10/100</f>
         <v>9.0299766211091384E-3</v>
       </c>
-      <c r="E27" s="59">
+      <c r="E27" s="57">
         <v>6.7678159943465903E-3</v>
       </c>
-      <c r="F27" s="59">
+      <c r="F27" s="57">
         <f>M10</f>
         <v>2.3311894913207675E-3</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C28" s="59">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C28" s="57">
         <v>1.7965202333326E-3</v>
       </c>
-      <c r="D28" s="59">
+      <c r="D28" s="57">
         <f>O13/100</f>
         <v>8.201083939198767E-4</v>
       </c>
-      <c r="E28" s="59">
+      <c r="E28" s="57">
         <v>1.15470053837925E-5</v>
       </c>
-      <c r="F28" s="59">
+      <c r="F28" s="57">
         <f>M13</f>
         <v>3.4226370599940202E-3</v>
       </c>
     </row>
-    <row r="35" spans="8:22" x14ac:dyDescent="0.25">
-      <c r="H35" s="86" t="s">
+    <row r="35" spans="8:22" x14ac:dyDescent="0.2">
+      <c r="H35" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="I35" s="86"/>
-      <c r="J35" s="86"/>
-      <c r="K35" s="86"/>
-      <c r="L35" s="86"/>
-      <c r="M35" s="86"/>
-      <c r="O35" s="86" t="s">
+      <c r="I35" s="60"/>
+      <c r="J35" s="60"/>
+      <c r="K35" s="60"/>
+      <c r="L35" s="60"/>
+      <c r="M35" s="60"/>
+      <c r="O35" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="P35" s="86"/>
-      <c r="Q35" s="86"/>
-      <c r="R35" s="86"/>
-      <c r="S35" s="86"/>
-      <c r="T35" s="86"/>
-      <c r="U35" s="86"/>
-      <c r="V35" s="86"/>
+      <c r="P35" s="60"/>
+      <c r="Q35" s="60"/>
+      <c r="R35" s="60"/>
+      <c r="S35" s="60"/>
+      <c r="T35" s="60"/>
+      <c r="U35" s="60"/>
+      <c r="V35" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="N16:U16"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="O35:V35"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="L4:L6"/>
+    <mergeCell ref="M10:M12"/>
+    <mergeCell ref="N10:N12"/>
+    <mergeCell ref="O10:O12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="L13:L15"/>
+    <mergeCell ref="M13:M15"/>
+    <mergeCell ref="N13:N15"/>
+    <mergeCell ref="O13:O15"/>
     <mergeCell ref="M4:M6"/>
     <mergeCell ref="N4:N6"/>
     <mergeCell ref="O4:O6"/>
@@ -6177,15 +6208,16 @@
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="L10:L12"/>
-    <mergeCell ref="M10:M12"/>
-    <mergeCell ref="N10:N12"/>
-    <mergeCell ref="O10:O12"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="L13:L15"/>
-    <mergeCell ref="M13:M15"/>
-    <mergeCell ref="N13:N15"/>
-    <mergeCell ref="O13:O15"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="L4:L6"/>
+    <mergeCell ref="N16:U16"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="O35:V35"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
